--- a/data/Event_Data_NNA02VR-101.xlsx
+++ b/data/Event_Data_NNA02VR-101.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-09-2569 12:06</t>
+          <t>14-10-2569 07:13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -468,14 +468,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28-08-2569 13:22</t>
+          <t>24-09-2569 12:06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22-08-2569 06:45</t>
+          <t>28-08-2569 13:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16-08-2569 23:22</t>
+          <t>22-08-2569 06:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -534,14 +534,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06-08-2569 03:24</t>
+          <t>16-08-2569 23:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -556,14 +556,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01-08-2569 17:29</t>
+          <t>06-08-2569 03:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T/L, ไม่พบสาเหตุ, จ่ายไฟ, 17.40</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20-07-2569 08:44</t>
+          <t>01-08-2569 17:29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t>T/L, ไม่พบสาเหตุ, จ่ายไฟ, 17.40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14-07-2569 09:46</t>
+          <t>20-07-2569 08:44</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10-07-2569 23:47</t>
+          <t>14-07-2569 09:46</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10-07-2569 19:43</t>
+          <t>10-07-2569 23:47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10-07-2569 02:44</t>
+          <t>10-07-2569 19:43</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -688,14 +688,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22-06-2569 20:25</t>
+          <t>10-07-2569 02:44</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,19 +705,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>T/L,กิ่งไม้หักพาดสายแรงสูง 120A เฟส ABC บ.หนองหาว ห่าง R = 20 กม., จ่ายไฟ, 20.35</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18-06-2569 17:02</t>
+          <t>22-06-2569 20:25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -732,14 +732,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 17.24</t>
+          <t>T/L,กิ่งไม้หักพาดสายแรงสูง 120A เฟส ABC บ.หนองหาว ห่าง R = 20 กม., จ่ายไฟ, 20.35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>22-03-2569 21:20</t>
+          <t>18-06-2569 17:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -754,14 +754,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>T/L สายแรงสูง 50ACSR ตกลูกถ้วยเฟส ABC บ.ก่อ จ่ายไฟ 22.09</t>
+          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 17.24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07-02-2569 11:58</t>
+          <t>22-03-2569 21:20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>T/L กฟจ.นครพนม เชือกว่าวพาดสายแรงสูง เฟส 50 ACSR บ้านดอนแดง หลัง R ประมาณ 7 กม.</t>
+          <t>T/L สายแรงสูง 50ACSR ตกลูกถ้วยเฟส ABC บ.ก่อ จ่ายไฟ 22.09</t>
         </is>
       </c>
     </row>
@@ -797,6 +797,28 @@
         </is>
       </c>
       <c r="D17" t="inlineStr">
+        <is>
+          <t>T/L กฟจ.นครพนม เชือกว่าวพาดสายแรงสูง เฟส 50 ACSR บ้านดอนแดง หลัง R ประมาณ 7 กม.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>07-02-2569 11:58</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NNA02VR-101</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>T/L</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>T/L กฟจ.นครพนม เชือกว่าวพาดสายแรงสูง เฟส 50 ACSR บ้านดอนแดง หลัง R ประมาณ 7 กม.</t>
         </is>
